--- a/气象/表格文件/多站记录或比较/阈值&连续 天数/国家站/国家站单冬昼温 -30 天数(达到5天).xlsx
+++ b/气象/表格文件/多站记录或比较/阈值&连续 天数/国家站/国家站单冬昼温 -30 天数(达到5天).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\文档\GIT SYNC\default\气象\表格文件\多站记录或比较\阈值&amp;连续 天数\国家站\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B539C743-A3AF-49EA-9CC8-3F11FC8004AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0DF4A9E-82AD-4503-B3DE-DD465DB693CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{63218F12-DAD6-491D-A45F-F499505C30A2}"/>
   </bookViews>
@@ -439,15 +439,6 @@
     </font>
     <font>
       <b/>
-      <sz val="10"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="20"/>
       <color theme="0"/>
       <name val="等线"/>
@@ -495,6 +486,15 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="0" tint="-0.249977111117893"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
@@ -682,37 +682,34 @@
     <xf numFmtId="17" fontId="14" fillId="6" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="19" fillId="3" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="17" fontId="20" fillId="3" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="19" fillId="4" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="17" fontId="20" fillId="4" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="19" fillId="7" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="17" fontId="20" fillId="7" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="19" fillId="5" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="17" fontId="20" fillId="5" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="17" fontId="22" fillId="5" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="21" fillId="5" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="8" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -721,8 +718,14 @@
     <xf numFmtId="17" fontId="14" fillId="8" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="17" fontId="23" fillId="6" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="22" fillId="6" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="2" borderId="8" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="3"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -730,6 +733,9 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -739,14 +745,8 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="2" borderId="8" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="3"/>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1087,206 +1087,206 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="60" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="27"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="25"/>
     </row>
     <row r="2" spans="1:7" ht="30.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="25" t="s">
+      <c r="B2" s="26"/>
+      <c r="C2" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="D2" s="26"/>
-      <c r="E2" s="28" t="s">
+      <c r="D2" s="28"/>
+      <c r="E2" s="21" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="35.25" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="10">
+      <c r="C3" s="9">
         <v>25</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="29">
+      <c r="E3" s="22">
         <v>-40.299999999999997</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="34.9" x14ac:dyDescent="0.35">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="12">
+      <c r="C4" s="11">
         <v>21</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="29">
+      <c r="E4" s="22">
         <v>-36</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="34.9" x14ac:dyDescent="0.35">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="11">
         <v>20</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="29">
+      <c r="E5" s="22">
         <v>-36</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="34.9" x14ac:dyDescent="0.35">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="12">
+      <c r="C6" s="11">
         <v>19</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="E6" s="29">
+      <c r="E6" s="22">
         <v>-39.1</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="34.9" x14ac:dyDescent="0.35">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="14">
+      <c r="C7" s="13">
         <v>17</v>
       </c>
-      <c r="D7" s="15" t="s">
+      <c r="D7" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="E7" s="29">
+      <c r="E7" s="22">
         <v>-34.9</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="34.9" x14ac:dyDescent="0.35">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="16">
+      <c r="C8" s="15">
         <v>15</v>
       </c>
-      <c r="D8" s="17" t="s">
+      <c r="D8" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="E8" s="29">
+      <c r="E8" s="22">
         <v>-34.9</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="34.9" x14ac:dyDescent="0.35">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="16">
+      <c r="C9" s="15">
         <v>14</v>
       </c>
-      <c r="D9" s="17" t="s">
+      <c r="D9" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="22">
         <v>-38.1</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="3"/>
     </row>
     <row r="10" spans="1:7" ht="34.9" x14ac:dyDescent="0.35">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="16">
+      <c r="C10" s="15">
         <v>13</v>
       </c>
-      <c r="D10" s="18" t="s">
+      <c r="D10" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="E10" s="29">
+      <c r="E10" s="22">
         <v>-36.299999999999997</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="34.9" x14ac:dyDescent="0.35">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="16">
+      <c r="C11" s="15">
         <v>13</v>
       </c>
-      <c r="D11" s="17" t="s">
+      <c r="D11" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="E11" s="29">
+      <c r="E11" s="22">
         <v>-37.6</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="34.9" x14ac:dyDescent="0.35">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="8" t="s">
         <v>12</v>
       </c>
       <c r="C12" s="6">
         <v>9</v>
       </c>
-      <c r="D12" s="21" t="s">
+      <c r="D12" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="E12" s="29">
+      <c r="E12" s="22">
         <v>-39.299999999999997</v>
       </c>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
     </row>
     <row r="13" spans="1:7" ht="34.9" x14ac:dyDescent="0.35">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="8" t="s">
         <v>13</v>
       </c>
       <c r="C13" s="6">
@@ -1295,17 +1295,17 @@
       <c r="D13" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E13" s="29">
+      <c r="E13" s="22">
         <v>-35.799999999999997</v>
       </c>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
     </row>
     <row r="14" spans="1:7" ht="34.9" x14ac:dyDescent="0.35">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="8" t="s">
         <v>33</v>
       </c>
       <c r="C14" s="6">
@@ -1314,15 +1314,15 @@
       <c r="D14" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E14" s="29">
+      <c r="E14" s="22">
         <v>-34.4</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="34.9" x14ac:dyDescent="0.35">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="8" t="s">
         <v>15</v>
       </c>
       <c r="C15" s="6">
@@ -1331,15 +1331,15 @@
       <c r="D15" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="E15" s="29">
+      <c r="E15" s="22">
         <v>-36.799999999999997</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="34.9" x14ac:dyDescent="0.35">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="8" t="s">
         <v>36</v>
       </c>
       <c r="C16" s="6">
@@ -1348,15 +1348,15 @@
       <c r="D16" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E16" s="29">
+      <c r="E16" s="22">
         <v>-35.5</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="34.9" x14ac:dyDescent="0.35">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="8" t="s">
         <v>9</v>
       </c>
       <c r="C17" s="6">
@@ -1365,15 +1365,15 @@
       <c r="D17" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E17" s="29">
+      <c r="E17" s="22">
         <v>-33.5</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="34.9" x14ac:dyDescent="0.35">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="B18" s="8" t="s">
         <v>37</v>
       </c>
       <c r="C18" s="6">
@@ -1382,94 +1382,94 @@
       <c r="D18" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E18" s="29">
+      <c r="E18" s="22">
         <v>-35.799999999999997</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="34.9" x14ac:dyDescent="0.35">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="C19" s="19">
+      <c r="C19" s="18">
         <v>6</v>
       </c>
-      <c r="D19" s="20" t="s">
+      <c r="D19" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="E19" s="29">
+      <c r="E19" s="22">
         <v>-33.9</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="34.9" x14ac:dyDescent="0.35">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="19">
+      <c r="C20" s="18">
         <v>6</v>
       </c>
-      <c r="D20" s="20" t="s">
+      <c r="D20" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="E20" s="29">
+      <c r="E20" s="22">
         <v>-36.9</v>
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
     </row>
     <row r="21" spans="1:7" ht="34.9" x14ac:dyDescent="0.35">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="B21" s="9" t="s">
+      <c r="B21" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C21" s="19">
+      <c r="C21" s="18">
         <v>5</v>
       </c>
-      <c r="D21" s="20" t="s">
+      <c r="D21" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="E21" s="29">
+      <c r="E21" s="22">
         <v>-34.700000000000003</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="34.9" x14ac:dyDescent="0.35">
-      <c r="A22" s="8" t="s">
+      <c r="A22" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="B22" s="9" t="s">
+      <c r="B22" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="C22" s="19">
+      <c r="C22" s="18">
         <v>5</v>
       </c>
-      <c r="D22" s="20" t="s">
+      <c r="D22" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="E22" s="29">
+      <c r="E22" s="22">
         <v>-36</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="34.9" x14ac:dyDescent="0.35">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="B23" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="C23" s="19">
+      <c r="C23" s="18">
         <v>5</v>
       </c>
-      <c r="D23" s="20" t="s">
+      <c r="D23" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="E23" s="29">
+      <c r="E23" s="22">
         <v>-34.9</v>
       </c>
     </row>
